--- a/output/pdf_financials_xlsx/TANA.xlsx
+++ b/output/pdf_financials_xlsx/TANA.xlsx
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.087205</v>
+        <v>0.148326</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.131482</v>
+        <v>0.184952</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.138208</v>
+        <v>0.198876</v>
       </c>
     </row>
     <row r="11">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.087205</v>
+        <v>-0.148326</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.131482</v>
+        <v>-0.184952</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.138208</v>
+        <v>-0.198876</v>
       </c>
     </row>
     <row r="12">
@@ -982,13 +982,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.06786</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.014591</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.001789</v>
       </c>
     </row>
     <row r="35">
@@ -1014,13 +1014,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.0015</v>
+        <v>0.06936</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.0015</v>
+        <v>0.016091</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.002</v>
+        <v>0.003789</v>
       </c>
     </row>
     <row r="37">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.06796000000000001</v>
+        <v>0.0001</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.014691</v>
+        <v>0.0001</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0</v>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E58" s="5" t="n">

--- a/output/pdf_financials_xlsx/TANA.xlsx
+++ b/output/pdf_financials_xlsx/TANA.xlsx
@@ -1523,10 +1523,10 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.107674</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.196001</v>
       </c>
     </row>
     <row r="68">
